--- a/outputs/44266.xlsx
+++ b/outputs/44266.xlsx
@@ -211,103 +211,103 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1062,7 +1062,7 @@
         <v>2007</v>
       </c>
       <c r="B2" s="24" t="n">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A2, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A2,Data!$4:$4,0)+1),"")</f>
         <v>8839097044.34167</v>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         <v>2008</v>
       </c>
       <c r="B3" s="24" t="n">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A3, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A3,Data!$4:$4,0)+1),"")</f>
         <v>100000000</v>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
         <v>2009</v>
       </c>
       <c r="B4" s="24" t="n">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A4, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A4,Data!$4:$4,0)+1),"")</f>
         <v>11000055156</v>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
         <v>2010</v>
       </c>
       <c r="B5" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A5, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A5,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
         <v>2011</v>
       </c>
       <c r="B6" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A6, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A6,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         <v>2012</v>
       </c>
       <c r="B7" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A7, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A7,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         <v>2013</v>
       </c>
       <c r="B8" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A8, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A8,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
         <v>2014</v>
       </c>
       <c r="B9" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A9, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A9,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>2015</v>
       </c>
       <c r="B10" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A10, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A10,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>2016</v>
       </c>
       <c r="B11" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A11, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A11,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         <v>2017</v>
       </c>
       <c r="B12" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Data!$14:$14, MATCH($A12, Data!$4:$4, 0)+1), "")</f>
+        <f aca="false">IFERROR(INDEX(Data!$14:$14,MATCH(A12,Data!$4:$4,0)+1),"")</f>
         <v/>
       </c>
     </row>
